--- a/data.xlsx
+++ b/data.xlsx
@@ -2652,7 +2652,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>205</v>
+        <v>179</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2742,7 +2742,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>موز</t>
+          <t>موز بلدي</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -2751,10 +2751,10 @@
         </is>
       </c>
       <c r="C2" s="6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E2" s="5" t="n"/>
       <c r="F2" s="6" t="inlineStr">
@@ -2773,7 +2773,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>تفاح أحمر</t>
+          <t>موز مستورد</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -2782,14 +2782,10 @@
         </is>
       </c>
       <c r="C3" s="6" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D3" s="6" t="n"/>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>صغير, وسط, كبير</t>
-        </is>
-      </c>
+      <c r="E3" s="5" t="n"/>
       <c r="F3" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -2806,7 +2802,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>برتقال</t>
+          <t>تفاح أحمر</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -2815,12 +2811,14 @@
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>34</v>
-      </c>
-      <c r="E4" s="5" t="n"/>
+        <v>90</v>
+      </c>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>صغير, وسط, كبير</t>
+        </is>
+      </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -2837,20 +2835,18 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>فراولة</t>
+          <t>تفاح أخضر</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>علبة 500 جم</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>52</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="D5" s="6" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="6" t="inlineStr">
         <is>
@@ -2859,7 +2855,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="H5" s="6" t="n"/>
@@ -2868,7 +2864,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>عنب أخضر</t>
+          <t>برتقال</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -2877,9 +2873,11 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>95</v>
-      </c>
-      <c r="D6" s="6" t="n"/>
+        <v>35</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>30</v>
+      </c>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="6" t="inlineStr">
         <is>
@@ -2888,7 +2886,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="H6" s="6" t="n"/>
@@ -2897,7 +2895,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>ليمون</t>
+          <t>برتقال أبو سرة</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -2908,9 +2906,7 @@
       <c r="C7" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="D7" s="6" t="n">
-        <v>39</v>
-      </c>
+      <c r="D7" s="6" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="6" t="inlineStr">
         <is>
@@ -2928,7 +2924,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>بطيخ</t>
+          <t>يوسفي</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -2937,13 +2933,13 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
@@ -2957,7 +2953,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>مانجو عويس</t>
+          <t>ليمون بلدي</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -2966,11 +2962,9 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>70</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>60</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="D9" s="6" t="n"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="6" t="inlineStr">
         <is>
@@ -2979,7 +2973,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="H9" s="6" t="n"/>
@@ -2988,7 +2982,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>جوافة</t>
+          <t>ليمون أضاليا</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -2997,7 +2991,7 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="5" t="n"/>
@@ -3017,7 +3011,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>رمان</t>
+          <t>جريب فروت</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -3026,7 +3020,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="5" t="n"/>
@@ -3046,7 +3040,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>كمثرى</t>
+          <t>جوافة</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -3055,7 +3049,7 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="D12" s="6" t="n"/>
       <c r="E12" s="5" t="n"/>
@@ -3075,7 +3069,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>تين</t>
+          <t>مانجو عويس</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -3084,9 +3078,11 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>80</v>
-      </c>
-      <c r="D13" s="6" t="n"/>
+        <v>85</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>75</v>
+      </c>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -3095,7 +3091,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="H13" s="6" t="n"/>
@@ -3104,7 +3100,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>كنتالوب</t>
+          <t>مانجو زبدية</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -3113,7 +3109,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="5" t="n"/>
@@ -3133,7 +3129,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>خوخ</t>
+          <t>عنب أخضر</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -3142,7 +3138,7 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D15" s="6" t="n"/>
       <c r="E15" s="5" t="n"/>
@@ -3162,7 +3158,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>مشمش</t>
+          <t>عنب أحمر</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -3171,7 +3167,7 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="D16" s="6" t="n"/>
       <c r="E16" s="5" t="n"/>
@@ -3191,7 +3187,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>عنب أحمر</t>
+          <t>رمان</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -3200,7 +3196,7 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="D17" s="6" t="n"/>
       <c r="E17" s="5" t="n"/>
@@ -3220,7 +3216,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>يوسفي</t>
+          <t>تين طازج</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -3229,7 +3225,7 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="D18" s="6" t="n"/>
       <c r="E18" s="5" t="n"/>
@@ -3249,18 +3245,20 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>كيوي</t>
+          <t>فراولة</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>علبة 500 جم</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>140</v>
-      </c>
-      <c r="D19" s="6" t="n"/>
+        <v>55</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>48</v>
+      </c>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="6" t="inlineStr">
         <is>
@@ -3269,7 +3267,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="H19" s="6" t="n"/>
@@ -3278,16 +3276,16 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>أناناس</t>
+          <t>بطيخ</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="D20" s="6" t="n"/>
       <c r="E20" s="5" t="n"/>
@@ -3307,7 +3305,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>بلح</t>
+          <t>شمام</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -3316,7 +3314,7 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="D21" s="6" t="n"/>
       <c r="E21" s="5" t="n"/>
@@ -3332,6 +3330,296 @@
       </c>
       <c r="H21" s="6" t="n"/>
       <c r="I21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>كمثرى</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>كيلو</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>خوخ</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>كيلو</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>مشمش</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>كيلو</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>كيوي</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>كيلو</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>140</v>
+      </c>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>أناناس</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>حبة</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="n"/>
+      <c r="I26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>بلح أحمر</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>كيلو</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>كاكا</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>كيلو</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>توت</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>علبة 250 جم</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="n"/>
+      <c r="I29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>جوز الهند الطازج</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>حبة</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="n"/>
+      <c r="I30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>بلح زغلول</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>كيلو</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="5" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:I300">
@@ -3374,7 +3662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3447,10 +3735,10 @@
         </is>
       </c>
       <c r="C2" s="6" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E2" s="5" t="n"/>
       <c r="F2" s="6" t="inlineStr">
@@ -3507,10 +3795,10 @@
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="6" t="inlineStr">
@@ -3558,7 +3846,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>جزر</t>
+          <t>بصل أبيض</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -3587,7 +3875,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>كوسة</t>
+          <t>ثوم بلدي</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -3596,7 +3884,7 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="D7" s="6" t="n"/>
       <c r="E7" s="5" t="n"/>
@@ -3616,7 +3904,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>باذنجان</t>
+          <t>جزر</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -3625,7 +3913,7 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="5" t="n"/>
@@ -3645,7 +3933,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>فلفل رومي</t>
+          <t>فلفل رومي أخضر</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -3654,7 +3942,7 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D9" s="6" t="n"/>
       <c r="E9" s="5" t="n"/>
@@ -3674,16 +3962,16 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>خس</t>
+          <t>فلفل ألوان</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>حزمة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="5" t="n"/>
@@ -3703,7 +3991,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>فاصوليا خضراء</t>
+          <t>فلفل حار</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -3712,7 +4000,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="5" t="n"/>
@@ -3732,7 +4020,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>بسلة</t>
+          <t>باذنجان أسود</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -3741,7 +4029,7 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="D12" s="6" t="n"/>
       <c r="E12" s="5" t="n"/>
@@ -3761,7 +4049,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>بامية</t>
+          <t>باذنجان رومي</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -3770,7 +4058,7 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="D13" s="6" t="n"/>
       <c r="E13" s="5" t="n"/>
@@ -3790,16 +4078,16 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>ملوخية</t>
+          <t>كوسة</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>حزمة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="5" t="n"/>
@@ -3819,16 +4107,16 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>سبانخ</t>
+          <t>قرنبيط</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>حزمة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D15" s="6" t="n"/>
       <c r="E15" s="5" t="n"/>
@@ -3877,16 +4165,16 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>قرنبيط</t>
+          <t>خس</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>حبة</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D17" s="6" t="n"/>
       <c r="E17" s="5" t="n"/>
@@ -3906,16 +4194,16 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>ثوم</t>
+          <t>جرجير</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>حزمة</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="D18" s="6" t="n"/>
       <c r="E18" s="5" t="n"/>
@@ -3935,16 +4223,16 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>بطاطا</t>
+          <t>بقدونس</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>حزمة</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D19" s="6" t="n"/>
       <c r="E19" s="5" t="n"/>
@@ -3964,7 +4252,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>جرجير</t>
+          <t>شبت</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -3973,7 +4261,7 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D20" s="6" t="n"/>
       <c r="E20" s="5" t="n"/>
@@ -3993,16 +4281,16 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>بنجر</t>
+          <t>كزبرة خضراء</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>حزمة</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D21" s="6" t="n"/>
       <c r="E21" s="5" t="n"/>
@@ -4018,6 +4306,327 @@
       </c>
       <c r="H21" s="6" t="n"/>
       <c r="I21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>نعناع</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>حزمة</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>ملوخية خضراء</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>حزمة</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>سبانخ</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>حزمة</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>بسلة</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>كيلو</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>فاصوليا خضراء</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>كيلو</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="n"/>
+      <c r="I26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>بنجر</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>كيلو</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>بامية</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>كيلو</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>بطاطا</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>كيلو</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="n"/>
+      <c r="I29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>ذرة</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>كيلو</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="n"/>
+      <c r="I30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>لفت</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>كيلو</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>فجل</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>حزمة</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="n"/>
+      <c r="I32" s="5" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:I300">
@@ -4060,7 +4669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4124,20 +4733,18 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>لب سوبر</t>
+          <t>لوز</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>250 جم</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="C2" s="6" t="n">
-        <v>160</v>
-      </c>
-      <c r="D2" s="6" t="n">
-        <v>145</v>
-      </c>
+        <v>520</v>
+      </c>
+      <c r="D2" s="6" t="n"/>
       <c r="E2" s="5" t="n"/>
       <c r="F2" s="6" t="inlineStr">
         <is>
@@ -4146,7 +4753,7 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="H2" s="6" t="n"/>
@@ -4155,18 +4762,20 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>لب أسمر</t>
+          <t>كاجو</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>250 جم</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="C3" s="6" t="n">
-        <v>95</v>
-      </c>
-      <c r="D3" s="6" t="n"/>
+        <v>600</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>549</v>
+      </c>
       <c r="E3" s="5" t="n"/>
       <c r="F3" s="6" t="inlineStr">
         <is>
@@ -4175,7 +4784,7 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="H3" s="6" t="n"/>
@@ -4184,25 +4793,19 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>فول سوداني</t>
+          <t>فستق</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>250 جم</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>70</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>62</v>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>سادة, مملح</t>
-        </is>
-      </c>
+        <v>700</v>
+      </c>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="5" t="n"/>
       <c r="F4" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -4219,16 +4822,16 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>لوز</t>
+          <t>بندق</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>250 جم</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>140</v>
+        <v>480</v>
       </c>
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="5" t="n"/>
@@ -4248,20 +4851,18 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>كاجو</t>
+          <t>عين جمل</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>250 جم</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>190</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>175</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="D6" s="6" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="6" t="inlineStr">
         <is>
@@ -4270,7 +4871,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="H6" s="6" t="n"/>
@@ -4279,16 +4880,16 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>فستق</t>
+          <t>فول سوداني محمص</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>250 جم</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="D7" s="6" t="n"/>
       <c r="E7" s="5" t="n"/>
@@ -4308,16 +4909,16 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>بندق</t>
+          <t>فول سوداني نيء</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>250 جم</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="5" t="n"/>
@@ -4337,20 +4938,18 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>عين جمل</t>
+          <t>لب سوبر</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>250 جم</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>150</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>138</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="D9" s="6" t="n"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="6" t="inlineStr">
         <is>
@@ -4368,16 +4967,16 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>زبيب</t>
+          <t>لب أسمر</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>250 جم</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="5" t="n"/>
@@ -4397,20 +4996,18 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>تمر</t>
+          <t>لب أبيض</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>500 جم</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>75</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>68</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="D11" s="6" t="n"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -4428,16 +5025,16 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>حمص الشام</t>
+          <t>لب سوداني</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>250 جم</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="D12" s="6" t="n"/>
       <c r="E12" s="5" t="n"/>
@@ -4457,20 +5054,18 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>مكس مكسرات</t>
+          <t>بذور دوار الشمس</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>300 جم</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>210</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>189</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="D13" s="6" t="n"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -4479,7 +5074,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="H13" s="6" t="n"/>
@@ -4488,16 +5083,16 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>جوز هند مبشور</t>
+          <t>حمص الشام</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>عبوة 100 جم</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="5" t="n"/>
@@ -4517,16 +5112,16 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>سمسم أبيض</t>
+          <t>زبيب</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>عبوة 250 جم</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>42</v>
+        <v>150</v>
       </c>
       <c r="D15" s="6" t="n"/>
       <c r="E15" s="5" t="n"/>
@@ -4546,16 +5141,16 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>عباد شمس مقشر</t>
+          <t>تمر مجدول</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>عبوة 250 جم</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>40</v>
+        <v>180</v>
       </c>
       <c r="D16" s="6" t="n"/>
       <c r="E16" s="5" t="n"/>
@@ -4575,16 +5170,16 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>بذور قرع</t>
+          <t>بلح سيوي</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>250 جم</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D17" s="6" t="n"/>
       <c r="E17" s="5" t="n"/>
@@ -4604,16 +5199,16 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>بذور كتان</t>
+          <t>قمر الدين</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>250 جم</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="D18" s="6" t="n"/>
       <c r="E18" s="5" t="n"/>
@@ -4633,16 +5228,16 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>مشمش مجفف</t>
+          <t>تين مجفف</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>250 جم</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>95</v>
+        <v>160</v>
       </c>
       <c r="D19" s="6" t="n"/>
       <c r="E19" s="5" t="n"/>
@@ -4662,16 +5257,16 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>تين مجفف</t>
+          <t>مشمش مجفف</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>250 جم</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>110</v>
+        <v>190</v>
       </c>
       <c r="D20" s="6" t="n"/>
       <c r="E20" s="5" t="n"/>
@@ -4691,16 +5286,16 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>جوز</t>
+          <t>جوز هند مبشور</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>250 جم</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="D21" s="6" t="n"/>
       <c r="E21" s="5" t="n"/>
@@ -4716,6 +5311,153 @@
       </c>
       <c r="H21" s="6" t="n"/>
       <c r="I21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>فشار ذرة</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>كيلو</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>خليط مكسرات</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>كيلو</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>350</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>320</v>
+      </c>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>ترمس</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>كيلو</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>سمسم</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>كيلو</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>كاجو بالملح</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>كيلو</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>620</v>
+      </c>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="n"/>
+      <c r="I26" s="5" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:I300">
@@ -4758,7 +5500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4822,7 +5564,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>شيبسي ملح</t>
+          <t>شيبسي صغير</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -4831,12 +5573,12 @@
         </is>
       </c>
       <c r="C2" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D2" s="6" t="n"/>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>ملح, جبنة, كاتشب, خل</t>
+          <t>جبنة, كاتشب, ملح وخل, شطة</t>
         </is>
       </c>
       <c r="F2" s="6" t="inlineStr">
@@ -4855,7 +5597,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>بطاطس بالجبنة</t>
+          <t>شيبسي كبير</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -4864,10 +5606,14 @@
         </is>
       </c>
       <c r="C3" s="6" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D3" s="6" t="n"/>
-      <c r="E3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>جبنة, كاتشب, ملح وخل, شطة</t>
+        </is>
+      </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -4884,21 +5630,23 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>بوشار</t>
+          <t>شيبسي عائلي</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيس</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="E4" s="5" t="n"/>
+        <v>35</v>
+      </c>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>جبنة, كاتشب, ملح وخل, شطة</t>
+        </is>
+      </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -4915,19 +5663,23 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>لبان</t>
+          <t>تايجر صغير</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيس</t>
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D5" s="6" t="n"/>
-      <c r="E5" s="5" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>جبنة, كاتشب, شطة</t>
+        </is>
+      </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -4944,7 +5696,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>نودلز</t>
+          <t>تايجر كبير</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -4953,12 +5705,12 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>دجاج, لحمة, شطة</t>
+          <t>جبنة, كاتشب, شطة</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -4977,7 +5729,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>ذرة مشوية</t>
+          <t>فوكس شيبس</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -4986,10 +5738,14 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7" s="6" t="n"/>
-      <c r="E7" s="5" t="n"/>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>جبنة, كاتشب, ملح</t>
+        </is>
+      </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -5006,19 +5762,23 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>بسكويت بالتمر</t>
+          <t>بيج شيبس</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيس</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="5" t="n"/>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>جبنة, كاتشب, ملح</t>
+        </is>
+      </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -5035,19 +5795,23 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>شيبسي بطاطس كبير</t>
+          <t>برينجلز</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>كيس</t>
+          <t>علبة 165 جم</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="D9" s="6" t="n"/>
-      <c r="E9" s="5" t="n"/>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>أصلي, جبنة, كريمة وبصل</t>
+        </is>
+      </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -5064,21 +5828,23 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>دوريتوس جبنة</t>
+          <t>دوريتوس</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>كيس 40 جم</t>
+          <t>كيس</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="E10" s="5" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>جبنة, حار</t>
+        </is>
+      </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -5086,7 +5852,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="H10" s="6" t="n"/>
@@ -5095,7 +5861,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>شيتوس</t>
+          <t>تشيتوس</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -5104,10 +5870,14 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D11" s="6" t="n"/>
-      <c r="E11" s="5" t="n"/>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>جبنة, كاتشب</t>
+        </is>
+      </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -5124,19 +5894,23 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>بسكويت أولكر</t>
+          <t>فشار ميكروويف</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>باكو</t>
+          <t>علبة</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D12" s="6" t="n"/>
-      <c r="E12" s="5" t="n"/>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>زبدة, كراميل</t>
+        </is>
+      </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -5153,19 +5927,23 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>ذرة مقرمشة</t>
+          <t>أوريو</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>كيس</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="5" t="n"/>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>فانيليا, شوكولاتة</t>
+        </is>
+      </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -5182,16 +5960,16 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>فشار ميكروويف</t>
+          <t>لوتس بسكويت</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>كيس</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="5" t="n"/>
@@ -5211,16 +5989,16 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>بسكويت مملح</t>
+          <t>ديجستيف</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>باكو</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="D15" s="6" t="n"/>
       <c r="E15" s="5" t="n"/>
@@ -5240,12 +6018,12 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>كراكرز جبنة</t>
+          <t>بسكويت بالتمر</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>باكو</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
@@ -5269,19 +6047,23 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>بطاطس أصابع</t>
+          <t>مولتو كرواسون</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>كيس</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
         <v>10</v>
       </c>
       <c r="D17" s="6" t="n"/>
-      <c r="E17" s="5" t="n"/>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>شوكولاتة, فانيليا, فراولة, كريمة</t>
+        </is>
+      </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -5289,7 +6071,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="H17" s="6" t="n"/>
@@ -5298,19 +6080,23 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>تورتيلا شيبس</t>
+          <t>بيك رولز</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>كيس</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D18" s="6" t="n"/>
-      <c r="E18" s="5" t="n"/>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>شوكولاتة, فانيليا</t>
+        </is>
+      </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -5327,19 +6113,23 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>مقرمشات حمص</t>
+          <t>تيفاني ويفر</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>كيس</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D19" s="6" t="n"/>
-      <c r="E19" s="5" t="n"/>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>شوكولاتة, فانيليا</t>
+        </is>
+      </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -5356,16 +6146,16 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>بسكويت شيكولاتة</t>
+          <t>تيفاني فنجان</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>باكو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20" s="6" t="n"/>
       <c r="E20" s="5" t="n"/>
@@ -5385,16 +6175,16 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>مقرمشات سمسم</t>
+          <t>جالاكسي</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>كيس</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="D21" s="6" t="n"/>
       <c r="E21" s="5" t="n"/>
@@ -5410,6 +6200,416 @@
       </c>
       <c r="H21" s="6" t="n"/>
       <c r="I21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>سنيكرز</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>قطعة</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>كادبوري ديري ميلك</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>قطعة</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>تويكس</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>قطعة</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>كيندر جوي</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>قطعة</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>شوكولاتة جالاكسي بالبندق</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>لوح</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="n"/>
+      <c r="I26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>مصاصة تشوبا تشوبس</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>قطعة</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>بيج بابل علكة</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>قطعة</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>هاريبو جيلي</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>كيس</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>دببة, خواتم, حروف</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="n"/>
+      <c r="I29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>كراميل</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>علبة</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="n"/>
+      <c r="I30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ملبن</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>كيس</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>سوداني حلو</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>كيس</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="n"/>
+      <c r="I32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>بطاطس شيبس سادة</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>كيس</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="n"/>
+      <c r="I33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>ذرة مقرمشة</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>كيس</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="n"/>
+      <c r="I34" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>قرمشة بالجبنة</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>كيس</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="n"/>
+      <c r="I35" s="5" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:I300">
@@ -5452,7 +6652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -5516,19 +6716,23 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>مياه معدنية</t>
+          <t>بيبسي زجاجة</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>زجاجة 1.5 لتر</t>
+          <t>زجاجة 1 لتر</t>
         </is>
       </c>
       <c r="C2" s="6" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D2" s="6" t="n"/>
-      <c r="E2" s="5" t="n"/>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>عادي, دايت</t>
+        </is>
+      </c>
       <c r="F2" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -5545,21 +6749,23 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>عصير برتقال</t>
+          <t>بيبسي علبة</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>عبوة 1 لتر</t>
+          <t>علبة 330 مل</t>
         </is>
       </c>
       <c r="C3" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="D3" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="E3" s="5" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>عادي, دايت</t>
+        </is>
+      </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -5567,7 +6773,7 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="H3" s="6" t="n"/>
@@ -5576,19 +6782,23 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>عصير مانجو</t>
+          <t>كوكاكولا زجاجة</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>عبوة 1 لتر</t>
+          <t>زجاجة 1 لتر</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
         <v>22</v>
       </c>
       <c r="D4" s="6" t="n"/>
-      <c r="E4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>عادي, زيرو</t>
+        </is>
+      </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -5605,7 +6815,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>كولا</t>
+          <t>كوكاكولا علبة</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -5614,10 +6824,14 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D5" s="6" t="n"/>
-      <c r="E5" s="5" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>عادي, زيرو</t>
+        </is>
+      </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -5634,16 +6848,16 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>ليمون غازي</t>
+          <t>سفن أب</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>علبة 330 مل</t>
+          <t>زجاجة 1 لتر</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="5" t="n"/>
@@ -5663,20 +6877,18 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>مشروب طاقة</t>
+          <t>سبرايت</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>علبة 250 مل</t>
+          <t>زجاجة 1 لتر</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>31</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="D7" s="6" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="6" t="inlineStr">
         <is>
@@ -5694,21 +6906,21 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>شاي مثلج</t>
+          <t>فانتا</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>زجاجة 500 مل</t>
+          <t>زجاجة 1 لتر</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>خوخ, ليمون</t>
+          <t>برتقال, فراولة</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -5727,19 +6939,23 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>لبن بالشوكولاتة</t>
+          <t>ميرندا</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>عبوة 250 مل</t>
+          <t>زجاجة 1 لتر</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D9" s="6" t="n"/>
-      <c r="E9" s="5" t="n"/>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>برتقال, تفاح</t>
+        </is>
+      </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -5756,21 +6972,23 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>مياه غازية كبيرة</t>
+          <t>شويبس</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>زجاجة 2 لتر</t>
+          <t>علبة 330 مل</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="E10" s="5" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>رمان, ليمون, أناناس</t>
+        </is>
+      </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -5778,7 +6996,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="H10" s="6" t="n"/>
@@ -5787,19 +7005,23 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>قهوة باردة</t>
+          <t>بيريل</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>علبة 250 مل</t>
+          <t>علبة 330 مل</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D11" s="6" t="n"/>
-      <c r="E11" s="5" t="n"/>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>سادة, تفاح, رمان</t>
+        </is>
+      </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -5816,19 +7038,23 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>كركديه</t>
+          <t>مياه معدنية كبيرة</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>زجاجة 500 مل</t>
+          <t>زجاجة 1.5 لتر</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D12" s="6" t="n"/>
-      <c r="E12" s="5" t="n"/>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>نستله, حياة, أكوافينا</t>
+        </is>
+      </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -5845,19 +7071,23 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>سوبيا</t>
+          <t>مياه معدنية صغيرة</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>زجاجة 500 مل</t>
+          <t>زجاجة 600 مل</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="5" t="n"/>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>نستله, حياة, أكوافينا</t>
+        </is>
+      </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -5874,20 +7104,18 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>بيبسي</t>
+          <t>مياه غازية بدون سكر</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>زجاجة 1 لتر</t>
+          <t>علبة</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>25</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="D14" s="6" t="n"/>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -5896,7 +7124,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="H14" s="6" t="n"/>
@@ -5905,19 +7133,23 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>كوكاكولا</t>
+          <t>عصير جهينة برتقال</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>زجاجة 1 لتر</t>
+          <t>علبة 1 لتر</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D15" s="6" t="n"/>
-      <c r="E15" s="5" t="n"/>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>برتقال, مانجو, جوافة, تفاح</t>
+        </is>
+      </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -5925,7 +7157,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="H15" s="6" t="n"/>
@@ -5934,16 +7166,16 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>سفن أب</t>
+          <t>عصير جهينة بيور</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>زجاجة 1 لتر</t>
+          <t>علبة 235 مل</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D16" s="6" t="n"/>
       <c r="E16" s="5" t="n"/>
@@ -5963,19 +7195,23 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>مياه نستله بيور لايف</t>
+          <t>ربيع عصير</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>زجاجة 1.5 لتر</t>
+          <t>علبة 235 مل</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D17" s="6" t="n"/>
-      <c r="E17" s="5" t="n"/>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>مانجو, جوافة, خوخ, تفاح</t>
+        </is>
+      </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -5992,16 +7228,16 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>عصير جهينة بيور مانجو</t>
+          <t>فيروز عصير</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>علبة 1 لتر</t>
+          <t>علبة 250 مل</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D18" s="6" t="n"/>
       <c r="E18" s="5" t="n"/>
@@ -6021,16 +7257,16 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>ريد بول</t>
+          <t>بيتي عصير</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>علبة 250 مل</t>
+          <t>علبة 1 لتر</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="D19" s="6" t="n"/>
       <c r="E19" s="5" t="n"/>
@@ -6050,19 +7286,23 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>عصير فريش برتقال</t>
+          <t>تانج</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>علبة 235 مل</t>
+          <t>كيس</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D20" s="6" t="n"/>
-      <c r="E20" s="5" t="n"/>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>برتقال, مانجو, ليمون</t>
+        </is>
+      </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -6079,16 +7319,16 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>عصير جوافة</t>
+          <t>نسكويك</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>عبوة 1 لتر</t>
+          <t>علبة 330 مل</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D21" s="6" t="n"/>
       <c r="E21" s="5" t="n"/>
@@ -6104,6 +7344,503 @@
       </c>
       <c r="H21" s="6" t="n"/>
       <c r="I21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>ريد بول</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>علبة 250 مل</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>ايس تي ليبتون</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>علبة</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>خوخ, ليمون</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>شاي ليبتون جاهز</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>زجاجة</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>نسكافيه جاهز</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>علبة</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>قهوة ساده بن العميد</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>علبة 200 جم</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="n"/>
+      <c r="I26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>عصير قصب</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>زجاجة</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>عصير ليمون</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>زجاجة</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>عصير مانجو</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>زجاجة</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="n"/>
+      <c r="I29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>عصير فراولة</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>زجاجة</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="n"/>
+      <c r="I30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>مياه فوارة</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>زجاجة</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>مشروب طاقة</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>علبة</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="n"/>
+      <c r="I32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>شاي أخضر مثلج</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>زجاجة</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="n"/>
+      <c r="I33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>كركديه جاهز</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>زجاجة</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="n"/>
+      <c r="I34" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>عرقسوس جاهز</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>زجاجة</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="n"/>
+      <c r="I35" s="5" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>تمر هندي جاهز</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>زجاجة</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="n"/>
+      <c r="I36" s="5" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>سحلب</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>علبة</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="n"/>
+      <c r="I37" s="5" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>حليب بالشوكولاتة</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>علبة 200 مل</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="n"/>
+      <c r="I38" s="5" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:I300">
@@ -6146,7 +7883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -6230,7 +7967,7 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="H2" s="6" t="n"/>
@@ -6239,23 +7976,19 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>مكرونة</t>
+          <t>أرز بسمتي</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>عبوة 400 جم</t>
+          <t>كيس 1 كجم</t>
         </is>
       </c>
       <c r="C3" s="6" t="n">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="D3" s="6" t="n"/>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>سباجيتي, بيني, قلم, أصابع</t>
-        </is>
-      </c>
+      <c r="E3" s="5" t="n"/>
       <c r="F3" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -6272,7 +8005,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>سكر</t>
+          <t>أرز كالروز</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -6281,7 +8014,7 @@
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="5" t="n"/>
@@ -6301,21 +8034,23 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>زيت عباد الشمس</t>
+          <t>مكرونة</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>زجاجة 1 لتر</t>
+          <t>عبوة 400 جم</t>
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>99</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>89</v>
-      </c>
-      <c r="E5" s="5" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>سباجيتي, بيني, قلم, أصابع, شعرية</t>
+        </is>
+      </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -6332,19 +8067,23 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>دقيق أبيض</t>
+          <t>مكرونة ماكا</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>كيس 1 كجم</t>
+          <t>عبوة 400 جم</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="5" t="n"/>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>سباجيتي, بيني, قلم, أصابع</t>
+        </is>
+      </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -6361,16 +8100,16 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>عدس أصفر</t>
+          <t>شعرية</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>كيس 500 جم</t>
+          <t>عبوة 400 جم</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="D7" s="6" t="n"/>
       <c r="E7" s="5" t="n"/>
@@ -6390,16 +8129,16 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>فول مدمس</t>
+          <t>سكر</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>علبة 400 جم</t>
+          <t>كيس 1 كجم</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="5" t="n"/>
@@ -6419,20 +8158,18 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>تونة</t>
+          <t>ملح</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>علبة 185 جم</t>
+          <t>كيس 1 كجم</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>37</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="D9" s="6" t="n"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="6" t="inlineStr">
         <is>
@@ -6441,7 +8178,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="H9" s="6" t="n"/>
@@ -6450,23 +8187,21 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>شاي</t>
+          <t>زيت عباد الشمس</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>علبة 100 كيس</t>
+          <t>زجاجة 1 لتر</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>عادي, بالنعناع, أخضر</t>
-        </is>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>89</v>
+      </c>
+      <c r="E10" s="5" t="n"/>
       <c r="F10" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -6474,7 +8209,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="H10" s="6" t="n"/>
@@ -6483,20 +8218,18 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>قهوة</t>
+          <t>زيت ذرة</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>برطمان 200 جم</t>
+          <t>زجاجة 1 لتر</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>64</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>56</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="D11" s="6" t="n"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -6514,16 +8247,16 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>صلصة طماطم</t>
+          <t>زيت زيتون</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>علبة 135 جم</t>
+          <t>زجاجة 500 مل</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>9</v>
+        <v>220</v>
       </c>
       <c r="D12" s="6" t="n"/>
       <c r="E12" s="5" t="n"/>
@@ -6543,20 +8276,18 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>مربى فراولة</t>
+          <t>سمن نباتي</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>برطمان 350 جم</t>
+          <t>علبة 1 كجم</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>31</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="D13" s="6" t="n"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -6574,20 +8305,18 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>مكرونة ريجينا 400 جم</t>
+          <t>سمن طبيعي</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>علبة 1 كجم</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>21</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="D14" s="6" t="n"/>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -6596,7 +8325,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="H14" s="6" t="n"/>
@@ -6605,16 +8334,16 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>أرز العلمين 1 كجم</t>
+          <t>دقيق أبيض</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>كيس</t>
+          <t>كيس 1 كجم</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D15" s="6" t="n"/>
       <c r="E15" s="5" t="n"/>
@@ -6634,20 +8363,18 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>زيت كريستال عباد الشمس</t>
+          <t>دقيق بلدي</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>زجاجة 1 لتر</t>
+          <t>كيس 1 كجم</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>99</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>89</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="D16" s="6" t="n"/>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="6" t="inlineStr">
         <is>
@@ -6656,7 +8383,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="H16" s="6" t="n"/>
@@ -6665,16 +8392,16 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>زيت عافية ذرة</t>
+          <t>عدس أصفر</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>زجاجة 1 لتر</t>
+          <t>كيس 500 جم</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>118</v>
+        <v>35</v>
       </c>
       <c r="D17" s="6" t="n"/>
       <c r="E17" s="5" t="n"/>
@@ -6694,16 +8421,16 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>شاي العروسة 40 جم</t>
+          <t>عدس بجبة</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>علبة</t>
+          <t>كيس 500 جم</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>11.5</v>
+        <v>38</v>
       </c>
       <c r="D18" s="6" t="n"/>
       <c r="E18" s="5" t="n"/>
@@ -6723,20 +8450,18 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>شاي ليبتون 40 جم</t>
+          <t>فول حراتي</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>علبة</t>
+          <t>كيس 500 جم</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>12</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="D19" s="6" t="n"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="6" t="inlineStr">
         <is>
@@ -6745,7 +8470,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="H19" s="6" t="n"/>
@@ -6754,16 +8479,16 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>نسكافيه كلاسيك 50 جم</t>
+          <t>حمص</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>برطمان</t>
+          <t>كيس 500 جم</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="D20" s="6" t="n"/>
       <c r="E20" s="5" t="n"/>
@@ -6783,16 +8508,16 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>فول معبأ</t>
+          <t>لوبيا</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>كيس 1 كجم</t>
+          <t>كيس 500 جم</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="D21" s="6" t="n"/>
       <c r="E21" s="5" t="n"/>
@@ -6812,16 +8537,16 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>دقيق معبأ</t>
+          <t>فاصوليا بيضاء</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>كيس 1 كجم</t>
+          <t>كيس 500 جم</t>
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="D22" s="6" t="n"/>
       <c r="E22" s="5" t="n"/>
@@ -6837,6 +8562,706 @@
       </c>
       <c r="H22" s="6" t="n"/>
       <c r="I22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>معجون طماطم</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>علبة 200 جم</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>صلصة طماطم</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>علبة 400 جم</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>تونة</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>علبة 185 جم</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>فول معلب</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>علبة 400 جم</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="n"/>
+      <c r="I26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>ذرة معلبة</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>علبة 340 جم</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>مخلل خيار</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>برطمان 700 جم</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>زيتون أسود</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>برطمان 330 جم</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="n"/>
+      <c r="I29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>شاي ليبتون</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>علبة 100 فتلة</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="n"/>
+      <c r="I30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>شاي العروسة</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>علبة 250 جم</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>نسكافيه</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>برطمان 200 جم</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>165</v>
+      </c>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="n"/>
+      <c r="I32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>بن</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>عبوة 200 جم</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="n"/>
+      <c r="I33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>عسل نحل</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>برطمان 500 جم</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="n"/>
+      <c r="I34" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>عسل أسود</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>برطمان 450 جم</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="n"/>
+      <c r="I35" s="5" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>طحينة</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>برطمان 500 جم</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="n"/>
+      <c r="I36" s="5" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>مربى</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>برطمان 400 جم</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>فراولة, مشمش, تين</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="n"/>
+      <c r="I37" s="5" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>خل</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>زجاجة 500 مل</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="n"/>
+      <c r="I38" s="5" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>ماء ورد</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>زجاجة 250 مل</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D39" s="6" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="n"/>
+      <c r="I39" s="5" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>خميرة</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>علبة</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="n"/>
+      <c r="I40" s="5" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>بيكنج بودر</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>علبة</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D41" s="6" t="n"/>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="n"/>
+      <c r="I41" s="5" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>فانيليا</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>علبة</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D42" s="6" t="n"/>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="n"/>
+      <c r="I42" s="5" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>نشا</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>علبة 200 جم</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D43" s="6" t="n"/>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="n"/>
+      <c r="I43" s="5" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>كاتشب</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>زجاجة 450 جم</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="D44" s="6" t="n"/>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="n"/>
+      <c r="I44" s="5" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>مايونيز</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>برطمان 400 جم</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="D45" s="6" t="n"/>
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="n"/>
+      <c r="I45" s="5" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>صلصة حارة</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>زجاجة</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D46" s="6" t="n"/>
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="n"/>
+      <c r="I46" s="5" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:I300">
@@ -6879,7 +9304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -6943,18 +9368,20 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>لبن كامل الدسم</t>
+          <t>لبن جهينة كامل الدسم</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>عبوة 1 لتر</t>
+          <t>علبة 1 لتر</t>
         </is>
       </c>
       <c r="C2" s="6" t="n">
-        <v>34</v>
-      </c>
-      <c r="D2" s="6" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>38</v>
+      </c>
       <c r="E2" s="5" t="n"/>
       <c r="F2" s="6" t="inlineStr">
         <is>
@@ -6972,20 +9399,18 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>لبن خالي الدسم</t>
+          <t>لبن جهينة نصف دسم</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>عبوة 1 لتر</t>
+          <t>علبة 1 لتر</t>
         </is>
       </c>
       <c r="C3" s="6" t="n">
-        <v>34</v>
-      </c>
-      <c r="D3" s="6" t="n">
-        <v>31</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="D3" s="6" t="n"/>
       <c r="E3" s="5" t="n"/>
       <c r="F3" s="6" t="inlineStr">
         <is>
@@ -7003,23 +9428,19 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>زبادي طبيعي</t>
+          <t>لبن جهينة خالي الدسم</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>عبوة 105 جم</t>
+          <t>علبة 1 لتر</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="D4" s="6" t="n"/>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>سادة, فراولة, عسل</t>
-        </is>
-      </c>
+      <c r="E4" s="5" t="n"/>
       <c r="F4" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -7036,20 +9457,18 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>جبنة رومي</t>
+          <t>لبن المراعي كامل الدسم</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>علبة 1 لتر</t>
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>190</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>175</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="D5" s="6" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="6" t="inlineStr">
         <is>
@@ -7058,7 +9477,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="H5" s="6" t="n"/>
@@ -7067,16 +9486,16 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>جبنة بيضاء</t>
+          <t>لبن بودرة نيدو</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>علبة 500 جم</t>
+          <t>علبة 400 جم</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>70</v>
+        <v>190</v>
       </c>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="5" t="n"/>
@@ -7096,20 +9515,18 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>جبنة مثلثات</t>
+          <t>لبن مكثف محلى</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>علبة 8 قطع</t>
+          <t>علبة 397 جم</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>34</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="D7" s="6" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="6" t="inlineStr">
         <is>
@@ -7132,11 +9549,11 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>علبة 200 جم</t>
+          <t>علبة 170 جم</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="5" t="n"/>
@@ -7156,20 +9573,18 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>زبدة</t>
+          <t>زبادي جهينة</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>قطعة 200 جم</t>
+          <t>علبة 105 جم</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>52</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="D9" s="6" t="n"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="6" t="inlineStr">
         <is>
@@ -7178,7 +9593,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="H9" s="6" t="n"/>
@@ -7187,16 +9602,16 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>بيض بلدي</t>
+          <t>زبادي كبير</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>كرتونة 30 بيضة</t>
+          <t>علبة 400 جم</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="5" t="n"/>
@@ -7207,7 +9622,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="H10" s="6" t="n"/>
@@ -7216,16 +9631,16 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>كريمة طبخ</t>
+          <t>زبادي يوناني</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>علبة 200 مل</t>
+          <t>علبة 150 جم</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="5" t="n"/>
@@ -7245,19 +9660,23 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>لبنة</t>
+          <t>زبادي بالفواكه</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>علبة 250 جم</t>
+          <t>علبة 125 جم</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D12" s="6" t="n"/>
-      <c r="E12" s="5" t="n"/>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>فراولة, موز, خوخ</t>
+        </is>
+      </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -7274,20 +9693,18 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>موزاريلا</t>
+          <t>لبن رايب</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>علبة 400 جم</t>
+          <t>علبة 1 كجم</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>120</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>105</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="D13" s="6" t="n"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="6" t="inlineStr">
         <is>
@@ -7305,20 +9722,18 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>لبن جهينة كامل الدسم</t>
+          <t>جبنة رومي</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>علبة 1 لتر</t>
+          <t>قطعة 250 جم</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>52</v>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>48</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="D14" s="6" t="n"/>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -7327,7 +9742,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="H14" s="6" t="n"/>
@@ -7336,16 +9751,16 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>لبن جهينة خالي الدسم</t>
+          <t>جبنة فيتا</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>علبة 1 لتر</t>
+          <t>علبة 500 جم</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="D15" s="6" t="n"/>
       <c r="E15" s="5" t="n"/>
@@ -7365,16 +9780,16 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>زبادي جهينة</t>
+          <t>جبنة بيضاء دومتي</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>علبة 105 جم</t>
+          <t>علبة 500 جم</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="D16" s="6" t="n"/>
       <c r="E16" s="5" t="n"/>
@@ -7394,16 +9809,16 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>جبنة دومتي فيتا</t>
+          <t>جبنة شيدر</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>علبة 500 جم</t>
+          <t>علبة 200 جم</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="D17" s="6" t="n"/>
       <c r="E17" s="5" t="n"/>
@@ -7423,16 +9838,16 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>جبنة كيري مثلثات</t>
+          <t>جبنة مثلثات</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>8 قطع</t>
+          <t>علبة 8 قطع</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D18" s="6" t="n"/>
       <c r="E18" s="5" t="n"/>
@@ -7452,20 +9867,18 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>بيض أبيض</t>
+          <t>جبنة كيري</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>كرتونة 30 بيضة</t>
+          <t>علبة 6 قطع</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>138</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>125</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="D19" s="6" t="n"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="6" t="inlineStr">
         <is>
@@ -7474,7 +9887,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="H19" s="6" t="n"/>
@@ -7483,16 +9896,16 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>زبدة لورباك</t>
+          <t>جبنة موزاريلا</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>عبوة 200 جم</t>
+          <t>كيس 200 جم</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>165</v>
+        <v>75</v>
       </c>
       <c r="D20" s="6" t="n"/>
       <c r="E20" s="5" t="n"/>
@@ -7512,16 +9925,16 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>جبنة شيدر شرائح</t>
+          <t>جبنة قريش</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>علبة 200 جم</t>
+          <t>علبة 250 جم</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="D21" s="6" t="n"/>
       <c r="E21" s="5" t="n"/>
@@ -7537,6 +9950,354 @@
       </c>
       <c r="H21" s="6" t="n"/>
       <c r="I21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>جبنة ريكوتا</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>علبة 250 جم</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>جبنة كريمي</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>علبة 500 جم</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>جبنة نابلسي</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>قطعة 250 جم</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>جبنة حلوم</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>قطعة 250 جم</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>لبنة</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>علبة 250 جم</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="n"/>
+      <c r="I26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>زبدة</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>قطعة 200 جم</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>زبدة لورباك</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>قطعة 200 جم</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>مارجرين</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>علبة 500 جم</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="n"/>
+      <c r="I29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>كريمة طبخ</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>علبة 250 مل</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="n"/>
+      <c r="I30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>بيض أبيض</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>كرتونة 30 بيضة</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>165</v>
+      </c>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>بيض بلدي</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>دستة</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="n"/>
+      <c r="I32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>بيض أحمر</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>كرتونة 30 بيضة</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="n"/>
+      <c r="I33" s="5" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:I300">
@@ -7579,7 +10340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -7648,7 +10409,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>5 أرغفة</t>
+          <t>ربطة 5 أرغفة</t>
         </is>
       </c>
       <c r="C2" s="6" t="n">
@@ -7663,7 +10424,7 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="H2" s="6" t="n"/>
@@ -7677,11 +10438,11 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>6 قطع</t>
+          <t>ربطة 6 أرغفة</t>
         </is>
       </c>
       <c r="C3" s="6" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D3" s="6" t="n"/>
       <c r="E3" s="5" t="n"/>
@@ -7701,25 +10462,19 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>توست</t>
+          <t>عيش شامي</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>عبوة 400 جم</t>
+          <t>ربطة 5 أرغفة</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>أبيض, أسمر</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="5" t="n"/>
       <c r="F4" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -7736,23 +10491,19 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>كرواسون</t>
+          <t>عيش توست أبيض</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D5" s="6" t="n"/>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>سادة, بالشوكولاتة, بالجبنة</t>
-        </is>
-      </c>
+      <c r="E5" s="5" t="n"/>
       <c r="F5" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -7760,7 +10511,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>نعم</t>
+          <t>لا</t>
         </is>
       </c>
       <c r="H5" s="6" t="n"/>
@@ -7769,16 +10520,16 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>باجيت</t>
+          <t>عيش توست أسمر</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>رغيف</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="5" t="n"/>
@@ -7798,16 +10549,16 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>بقسماط</t>
+          <t>عيش برجر</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>عبوة 200 جم</t>
+          <t>عبوة 6 أرغفة</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="D7" s="6" t="n"/>
       <c r="E7" s="5" t="n"/>
@@ -7827,16 +10578,16 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>عيش شامي</t>
+          <t>عيش هوت دوج</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>8 أرغفة</t>
+          <t>عبوة 6 أرغفة</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="5" t="n"/>
@@ -7856,20 +10607,18 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>رولز صغير</t>
+          <t>عيش لقمة</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>عبوة 10 قطع</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>19</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="D9" s="6" t="n"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="6" t="inlineStr">
         <is>
@@ -7887,16 +10636,16 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>توست بيمبو أبيض</t>
+          <t>كايزر</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>كيس</t>
+          <t>عبوة 6 أرغفة</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="5" t="n"/>
@@ -7916,16 +10665,16 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>كرواسون بالجبنة</t>
+          <t>بقسماط</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة 250 جم</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="5" t="n"/>
@@ -7945,16 +10694,16 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>بيتي فور</t>
+          <t>كعك</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>علبة</t>
+          <t>كيس</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D12" s="6" t="n"/>
       <c r="E12" s="5" t="n"/>
@@ -7974,16 +10723,16 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>بيجل بالسمسم</t>
+          <t>بسكويت صغير</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>كيس</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D13" s="6" t="n"/>
       <c r="E13" s="5" t="n"/>
@@ -8003,16 +10752,16 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>عيش سن</t>
+          <t>كرواسون سادة</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>5 أرغفة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="5" t="n"/>
@@ -8032,7 +10781,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>كايزر</t>
+          <t>كرواسون شوكولاتة</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -8041,7 +10790,7 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D15" s="6" t="n"/>
       <c r="E15" s="5" t="n"/>
@@ -8061,16 +10810,16 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>خبز برجر</t>
+          <t>كيك سادة</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>عبوة 4 قطع</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D16" s="6" t="n"/>
       <c r="E16" s="5" t="n"/>
@@ -8090,16 +10839,16 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>خبز بيتا</t>
+          <t>كيك شوكولاتة</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D17" s="6" t="n"/>
       <c r="E17" s="5" t="n"/>
@@ -8119,16 +10868,16 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>رغيف شوفان</t>
+          <t>كب كيك</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>رغيف</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D18" s="6" t="n"/>
       <c r="E18" s="5" t="n"/>
@@ -8148,16 +10897,16 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>فطيرة جبنة</t>
+          <t>كيك برتقال</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="D19" s="6" t="n"/>
       <c r="E19" s="5" t="n"/>
@@ -8177,12 +10926,12 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>رول قرفة</t>
+          <t>بسكويت أسمر</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
@@ -8206,16 +10955,16 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>بسكويت زبدة</t>
+          <t>دونتس</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>عبوة 200 جم</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D21" s="6" t="n"/>
       <c r="E21" s="5" t="n"/>
@@ -8231,6 +10980,238 @@
       </c>
       <c r="H21" s="6" t="n"/>
       <c r="I21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>فطير مشلتت</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>قطعة</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>بيتزا جاهزة</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>قطعة</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>ساندوتش جبنة</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>قطعة</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>كحك</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>كيلو</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>بسبوسة</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>قطعة</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="n"/>
+      <c r="I26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>جاتوه</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>قطعة</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>فطيرة بالجبنة</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>قطعة</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>فطيرة بالسبانخ</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>قطعة</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="n"/>
+      <c r="I29" s="5" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:I300">

--- a/data.xlsx
+++ b/data.xlsx
@@ -45,7 +45,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +55,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002B463C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005A3114"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -102,6 +107,9 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -985,12 +993,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>الشيت</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>الشرح</t>
         </is>
@@ -1160,7 +1168,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001F4D2E"/>
+    <tabColor rgb="00DE5718"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1179,47 +1187,47 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>الاسم</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>الوحدة</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>السعر الأساسي</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>السعر بعد الخصم</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>الأنواع</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>متوفر</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>عروض اليوم</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>شارة</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>صورة</t>
         </is>
@@ -1848,7 +1856,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001F4D2E"/>
+    <tabColor rgb="005A3114"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1867,47 +1875,47 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>الاسم</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>الوحدة</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>السعر الأساسي</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>السعر بعد الخصم</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>الأنواع</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>متوفر</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>عروض اليوم</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>شارة</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>صورة</t>
         </is>
@@ -2559,27 +2567,27 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>ظاهر</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>الباقة</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>المنتجات</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>سعر الباقة</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>وصف</t>
         </is>
@@ -2693,47 +2701,47 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>الاسم</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>الوحدة</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>السعر الأساسي</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>السعر بعد الخصم</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>الأنواع</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>متوفر</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>عروض اليوم</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>شارة</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>صورة</t>
         </is>
@@ -3658,7 +3666,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="003F7D2B"/>
+    <tabColor rgb="00F9B914"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -3677,47 +3685,47 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>الاسم</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>الوحدة</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>السعر الأساسي</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>السعر بعد الخصم</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>الأنواع</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>متوفر</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>عروض اليوم</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>شارة</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>صورة</t>
         </is>
@@ -4684,47 +4692,47 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>الاسم</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>الوحدة</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>السعر الأساسي</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>السعر بعد الخصم</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>الأنواع</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>متوفر</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>عروض اليوم</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>شارة</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>صورة</t>
         </is>
@@ -5496,7 +5504,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="008DBF5A"/>
+    <tabColor rgb="005A3114"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -5515,47 +5523,47 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>الاسم</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>الوحدة</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>السعر الأساسي</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>السعر بعد الخصم</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>الأنواع</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>متوفر</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>عروض اليوم</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>شارة</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>صورة</t>
         </is>
@@ -6648,7 +6656,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="003F7D2B"/>
+    <tabColor rgb="00F9B914"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -6667,47 +6675,47 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>الاسم</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>الوحدة</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>السعر الأساسي</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>السعر بعد الخصم</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>الأنواع</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>متوفر</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>عروض اليوم</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>شارة</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>صورة</t>
         </is>
@@ -7898,47 +7906,47 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>الاسم</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>الوحدة</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>السعر الأساسي</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>السعر بعد الخصم</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>الأنواع</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>متوفر</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>عروض اليوم</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>شارة</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>صورة</t>
         </is>
@@ -9319,47 +9327,47 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>الاسم</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>الوحدة</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>السعر الأساسي</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>السعر بعد الخصم</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>الأنواع</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>متوفر</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>عروض اليوم</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>شارة</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>صورة</t>
         </is>
@@ -10336,7 +10344,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="008DBF5A"/>
+    <tabColor rgb="00F9B914"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -10355,47 +10363,47 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>الاسم</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>الوحدة</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>السعر الأساسي</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>السعر بعد الخصم</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>الأنواع</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>متوفر</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>عروض اليوم</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>شارة</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>صورة</t>
         </is>
